--- a/Repartition_couts.xlsx
+++ b/Repartition_couts.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/79fc430203973324/TravauxMetriques/IIm/Passion IIm/PupitreLigne/AlimLigne_PassionIIm/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{48C7A40A-BED0-409D-895B-8CC7347D8572}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="74" documentId="8_{48C7A40A-BED0-409D-895B-8CC7347D8572}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7B7EA6F8-EA7E-423E-ABF2-15CEA1AE76D5}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{CB5EFA0C-1501-4308-95E7-4D3D48E49409}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{CB5EFA0C-1501-4308-95E7-4D3D48E49409}"/>
   </bookViews>
   <sheets>
-    <sheet name="Budget" sheetId="1" r:id="rId1"/>
+    <sheet name="Offre" sheetId="1" r:id="rId1"/>
+    <sheet name="Compte" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
   <si>
     <t>Fred</t>
   </si>
@@ -69,6 +70,27 @@
   </si>
   <si>
     <t>Sous-total</t>
+  </si>
+  <si>
+    <t>Cout</t>
+  </si>
+  <si>
+    <t>Digikey</t>
+  </si>
+  <si>
+    <t>Aliexpress</t>
+  </si>
+  <si>
+    <t>Conrad (est)</t>
+  </si>
+  <si>
+    <t>stock (est)</t>
+  </si>
+  <si>
+    <t>3D (est)</t>
+  </si>
+  <si>
+    <t>PCB (est)</t>
   </si>
 </sst>
 </file>
@@ -78,7 +100,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;CHF&quot;_-;\-* #,##0.00\ &quot;CHF&quot;_-;_-* &quot;-&quot;??\ &quot;CHF&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -89,6 +111,13 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="5" tint="-0.249977111117893"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -115,9 +144,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Monétaire" xfId="1" builtinId="4"/>
@@ -453,7 +484,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B7D1F00-7946-490B-8C6F-469A4946F0E5}">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="6" max="7" width="11.77734375" bestFit="1" customWidth="1"/>
@@ -572,6 +603,84 @@
         <v>130</v>
       </c>
     </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G8" s="2">
+        <f>SUM(G4:G6)</f>
+        <v>585</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D7A33B5-99AE-4E6F-A3BC-72E14FCBC62C}">
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2">
+        <v>77.349999999999994</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3">
+        <v>88.51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="3">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <f>SUM(B2:B7)</f>
+        <v>525.86</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Repartition_couts.xlsx
+++ b/Repartition_couts.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/79fc430203973324/TravauxMetriques/IIm/Passion IIm/PupitreLigne/AlimLigne_PassionIIm/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="74" documentId="8_{48C7A40A-BED0-409D-895B-8CC7347D8572}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7B7EA6F8-EA7E-423E-ABF2-15CEA1AE76D5}"/>
+  <xr:revisionPtr revIDLastSave="79" documentId="8_{48C7A40A-BED0-409D-895B-8CC7347D8572}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{261B8A03-D56E-4FD4-8B7D-557C1A7E012E}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{CB5EFA0C-1501-4308-95E7-4D3D48E49409}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{CB5EFA0C-1501-4308-95E7-4D3D48E49409}"/>
   </bookViews>
   <sheets>
     <sheet name="Offre" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
   <si>
     <t>Fred</t>
   </si>
@@ -91,6 +91,9 @@
   </si>
   <si>
     <t>PCB (est)</t>
+  </si>
+  <si>
+    <t>Marge (est)</t>
   </si>
 </sst>
 </file>
@@ -144,11 +147,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Monétaire" xfId="1" builtinId="4"/>
@@ -485,12 +489,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B7D1F00-7946-490B-8C6F-469A4946F0E5}">
   <dimension ref="A1:G8"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="6" max="7" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="11.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>1</v>
       </c>
@@ -510,7 +514,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B2">
         <v>45</v>
       </c>
@@ -524,7 +528,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -537,7 +541,7 @@
       </c>
       <c r="G3" s="1"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -559,7 +563,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -581,7 +585,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -603,7 +607,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="G8" s="2">
         <f>SUM(G4:G6)</f>
         <v>585</v>
@@ -616,69 +620,87 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D7A33B5-99AE-4E6F-A3BC-72E14FCBC62C}">
-  <dimension ref="A1:B10"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:B12"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="11.85546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="1">
         <v>77.349999999999994</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
-      <c r="B3">
-        <v>88.51</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B3" s="1">
+        <v>100.61</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="4">
         <v>230</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="4">
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="4">
         <v>43</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="4">
         <v>66</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B8" s="1"/>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B9" s="1"/>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="1">
         <f>SUM(B2:B7)</f>
-        <v>525.86</v>
+        <v>537.96</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" s="2">
+        <f>Offre!G8-B10</f>
+        <v>47.039999999999964</v>
       </c>
     </row>
   </sheetData>

--- a/Repartition_couts.xlsx
+++ b/Repartition_couts.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/79fc430203973324/TravauxMetriques/IIm/Passion IIm/PupitreLigne/AlimLigne_PassionIIm/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="79" documentId="8_{48C7A40A-BED0-409D-895B-8CC7347D8572}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{261B8A03-D56E-4FD4-8B7D-557C1A7E012E}"/>
+  <xr:revisionPtr revIDLastSave="82" documentId="8_{48C7A40A-BED0-409D-895B-8CC7347D8572}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8257A165-909C-4DBC-8C20-9EE8118C267B}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{CB5EFA0C-1501-4308-95E7-4D3D48E49409}"/>
+    <workbookView xWindow="204" yWindow="696" windowWidth="21600" windowHeight="12528" activeTab="1" xr2:uid="{CB5EFA0C-1501-4308-95E7-4D3D48E49409}"/>
   </bookViews>
   <sheets>
     <sheet name="Offre" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
   <si>
     <t>Fred</t>
   </si>
@@ -72,9 +72,6 @@
     <t>Sous-total</t>
   </si>
   <si>
-    <t>Cout</t>
-  </si>
-  <si>
     <t>Digikey</t>
   </si>
   <si>
@@ -94,6 +91,12 @@
   </si>
   <si>
     <t>Marge (est)</t>
+  </si>
+  <si>
+    <t>Conrad 1</t>
+  </si>
+  <si>
+    <t>Depenses</t>
   </si>
 </sst>
 </file>
@@ -489,12 +492,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B7D1F00-7946-490B-8C6F-469A4946F0E5}">
   <dimension ref="A1:G8"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="6" max="7" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="11.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>1</v>
       </c>
@@ -514,7 +517,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B2">
         <v>45</v>
       </c>
@@ -528,7 +531,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -541,7 +544,7 @@
       </c>
       <c r="G3" s="1"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -563,7 +566,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -585,7 +588,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -607,7 +610,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="G8" s="2">
         <f>SUM(G4:G6)</f>
         <v>585</v>
@@ -620,86 +623,92 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D7A33B5-99AE-4E6F-A3BC-72E14FCBC62C}">
-  <dimension ref="A1:B12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>11</v>
       </c>
       <c r="B2" s="1">
         <v>77.349999999999994</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1">
         <v>100.61</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="1"/>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="4">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="4">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="4">
+      <c r="B6" s="4">
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="4">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>15</v>
       </c>
       <c r="B7" s="4">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="4">
         <v>66</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B8" s="1"/>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B9" s="1"/>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B10" s="1"/>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="1">
-        <f>SUM(B2:B7)</f>
+      <c r="B11" s="1">
+        <f>SUM(B2:B8)</f>
         <v>537.96</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" s="2">
-        <f>Offre!G8-B10</f>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="2">
+        <f>Offre!G8-B11</f>
         <v>47.039999999999964</v>
       </c>
     </row>
